--- a/Result/profitability/2451.xlsx
+++ b/Result/profitability/2451.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.02</v>
       </c>
       <c r="M2" t="n">
-        <v>4.345</v>
+        <v>7.706250000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>38.935</v>
+        <v>44.92625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.62</v>
       </c>
       <c r="M3" t="n">
-        <v>4.44625</v>
+        <v>7.78</v>
       </c>
       <c r="N3" t="n">
-        <v>36.8975</v>
+        <v>43.42749999999999</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.63</v>
       </c>
       <c r="M4" t="n">
-        <v>4.52125</v>
+        <v>7.875</v>
       </c>
       <c r="N4" t="n">
-        <v>34.53874999999999</v>
+        <v>40.56375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.6</v>
       </c>
       <c r="M5" t="n">
-        <v>4.6125</v>
+        <v>7.9525</v>
       </c>
       <c r="N5" t="n">
-        <v>32.295</v>
+        <v>37.6325</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>2.3</v>
       </c>
       <c r="M6" t="n">
-        <v>4.7775</v>
+        <v>7.8</v>
       </c>
       <c r="N6" t="n">
-        <v>30.33375</v>
+        <v>34.31125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>2.31</v>
       </c>
       <c r="M7" t="n">
-        <v>4.62625</v>
+        <v>7.138749999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>27.315</v>
+        <v>29.24125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>2.74</v>
       </c>
       <c r="M8" t="n">
-        <v>4.01875</v>
+        <v>5.114999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>21.89875</v>
+        <v>21.97875</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2451</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>18815</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4321</v>
+      </c>
+      <c r="E75" t="n">
+        <v>14494</v>
+      </c>
+      <c r="F75" t="n">
+        <v>77.03</v>
+      </c>
+      <c r="G75" t="n">
+        <v>14127</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>75.08%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>636</v>
+      </c>
+      <c r="J75" t="n">
+        <v>14763</v>
+      </c>
+      <c r="K75" t="n">
+        <v>11897</v>
+      </c>
+      <c r="L75" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="M75" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="N75" t="n">
+        <v>47.1625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.4632857897517169</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.6400000000000006</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.008378059955491457</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>26.72</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>27.26530612244898</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.243810078648413</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
